--- a/app/assets/template.xlsx
+++ b/app/assets/template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,20 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <i val="1"/>
       <color rgb="00F5ECD8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F5ECD8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00C9D2E0"/>
       <sz val="11"/>
     </font>
     <font>
@@ -45,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B0B0E"/>
-        <bgColor rgb="000B0B0E"/>
+        <fgColor rgb="001A1A22"/>
+        <bgColor rgb="001A1A22"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B6BFF"/>
-        <bgColor rgb="002B6BFF"/>
+        <fgColor rgb="000B0B0E"/>
+        <bgColor rgb="000B0B0E"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,18 +95,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -178,49 +194,94 @@
     <author>App Iter</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: DD/MM/AAAA</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: 1-99</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: Ex: PTBIC</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: ICAO 4 letras</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: ICAO 4 letras</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: HH:MM</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: Observação livre</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: Milhas náuticas</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Formato: HH:MM</t>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>DD/MM/AAAA
+[Obrigatório]</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>Inteiro 1-99
+[Obrigatório]</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>Escolha uma opção do dropdown
+[Obrigatório]</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>Código ANAC do aluno (8 dígitos). Obrigatório se Função = Instrutor Voo ou Instrutor de voo em solo. Vazio nas demais Funções.
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>Sim/Não. Marque Sim apenas se Função = Piloto em Comando E o voo foi dentro de curso de piloto comercial aprovado pela ANAC com instrutor a bordo.
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>Texto livre opcional
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>Milhas náuticas (inteiro)
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>Matrícula da aeronave (até 5 chars, ex.: PTBIC)
+[Obrigatório]</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Aeródromo de origem — ICAO 4 letras (ex.: SBSP)
+[Obrigatório]</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>Aeródromo de destino — ICAO 4 letras
+[Obrigatório]</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>HH:MM. Pelo menos um de Diurno ou Noturno deve estar preenchido.
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>HH:MM. Pelo menos um de Diurno ou Noturno deve estar preenchido.
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>HH:MM — tempo de navegação
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>HH:MM — Instrumento Real (IFR efetivo)
+[Opcional]</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>HH:MM — instrução IFR simulada sob capota
+[Opcional]</t>
       </text>
     </comment>
   </commentList>
@@ -516,107 +577,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Dados do vôo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tempo de vôo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>POUSOS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>FUNCAO</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>ANAC_ALUNO</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>CURSO_COMERCIAL</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACOES</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>MILHAS_NAV</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>MATRICULA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>ORIGEM</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>DESTINO</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>HORAS</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>OBS</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>MILHAS_NAV</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>HORAS_NAV</t>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>NOTURNO</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>NAVEGACAO</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>INSTRUMENTO</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>SOB_CAPOTA</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Piloto em Comando</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Translado</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>PTBIC</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>SBSP</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>SBKP</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>00:45</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Translado</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:O1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C3:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Função inválida" error="Escolha uma das opções: Instrutor Voo, Piloto em Comando, Piloto em Instrução, Instrutor de voo em solo, Co-Piloto Single Pilot, Co-Piloto Single Pilot com co-piloto por questão regulamentar, Co-Piloto Dual Pilot." promptTitle="Função a bordo" prompt="Clique na seta e escolha uma opção" type="list">
+      <formula1>"Instrutor Voo,Piloto em Comando,Piloto em Instrução,Instrutor de voo em solo,Co-Piloto Single Pilot,Co-Piloto Single Pilot com co-piloto, por questão regulamentar,Co-Piloto Dual Pilot"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Use 'Sim' ou 'Não' (vazio é tratado como 'Não')." promptTitle="Curso comercial" prompt="Sim apenas se Função = Piloto em Comando" type="list">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/app/assets/template.xlsx
+++ b/app/assets/template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -703,13 +703,21 @@
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Translado</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>PTBIC</t>
@@ -730,10 +738,26 @@
           <t>00:45</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
